--- a/public/Lynn_River_final_sku_standardised.xlsx
+++ b/public/Lynn_River_final_sku_standardised.xlsx
@@ -12172,6 +12172,7 @@
   <dimension ref="A1:L1529"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
+    <col min="4" max="4" width="104.428571428571" customWidth="1"/>
     <col min="7" max="7" width="14.8571428571429" customWidth="1"/>
     <col min="8" max="8" width="22.1428571428571" customWidth="1"/>
     <col min="9" max="9" width="26.5714285714286" customWidth="1"/>
